--- a/output/isabel-cohorts/구성관반_총점_성장.xlsx
+++ b/output/isabel-cohorts/구성관반_총점_성장.xlsx
@@ -11,6 +11,7 @@
     <sheet name="총점 성장 요약" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="고1 모의고사" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="고2 모의고사" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="고3 모의고사·수능" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
   <si>
     <r>
       <rPr>
@@ -86,7 +87,41 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2(</t>
+      <t xml:space="preserve">2 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -155,6 +190,40 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">2 86.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점 → 고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수능 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">92.3</t>
     </r>
     <r>
       <rPr>
@@ -258,7 +327,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+19.8</t>
+      <t xml:space="preserve">+25.2</t>
     </r>
     <r>
       <rPr>
@@ -561,6 +630,56 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">모의고사
+평균</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수능
 평균</t>
     </r>
   </si>
@@ -3438,6 +3557,641 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구성관 반 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수능 총점 변화</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 시험 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 반 평균 총점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">92.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">■ 고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사는 중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">구성관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">송지효 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점 만점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">신준섭 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">87</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">박주연 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">82</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">명 모두 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급 이상입니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모의고사는 성적표에 아직 기록이 없습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">중</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">차 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2025)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
     </r>
   </si>
 </sst>
@@ -3780,7 +4534,7 @@
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF17403D"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -3875,9 +4629,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'총점 성장 요약'!$B$8:$D$8</c:f>
+              <c:f>'총점 성장 요약'!$B$8:$E$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>중1 첫 시험</c:v>
                 </c:pt>
@@ -3887,6 +4641,10 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>고2 모의고사
+평균</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>고3 모의고사+수능
 평균</c:v>
                 </c:pt>
               </c:strCache>
@@ -3894,10 +4652,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'총점 성장 요약'!$B$13:$D$13</c:f>
+              <c:f>'총점 성장 요약'!$B$13:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>67</c:v>
                 </c:pt>
@@ -3906,6 +4664,9 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>86.8125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>92.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3913,11 +4674,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="23231105"/>
-        <c:axId val="88476861"/>
+        <c:axId val="40489550"/>
+        <c:axId val="51854719"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="23231105"/>
+        <c:axId val="40489550"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3949,7 +4710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88476861"/>
+        <c:crossAx val="51854719"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3957,7 +4718,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88476861"/>
+        <c:axId val="51854719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4001,7 +4762,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23231105"/>
+        <c:crossAx val="40489550"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4361,13 +5122,109 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'총점 성장 요약'!E8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>고3 모의고사+수능
+평균</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="17403d"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="0" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'총점 성장 요약'!$A$9:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>구성관</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>송지효</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>신준섭</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>박주연</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'총점 성장 요약'!$E$9:$E$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>87</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>82</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="58212398"/>
-        <c:axId val="11148794"/>
+        <c:axId val="38058538"/>
+        <c:axId val="8728869"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58212398"/>
+        <c:axId val="38058538"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4399,7 +5256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11148794"/>
+        <c:crossAx val="8728869"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4407,7 +5264,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11148794"/>
+        <c:axId val="8728869"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4451,7 +5308,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58212398"/>
+        <c:crossAx val="38058538"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5195,11 +6052,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="67542761"/>
-        <c:axId val="96964975"/>
+        <c:axId val="91824569"/>
+        <c:axId val="94356926"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="67542761"/>
+        <c:axId val="91824569"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5231,7 +6088,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96964975"/>
+        <c:crossAx val="94356926"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5239,7 +6096,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96964975"/>
+        <c:axId val="94356926"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5317,7 +6174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67542761"/>
+        <c:crossAx val="91824569"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -5617,11 +6474,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="21417065"/>
-        <c:axId val="8198284"/>
+        <c:axId val="50580274"/>
+        <c:axId val="89593125"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21417065"/>
+        <c:axId val="50580274"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5653,7 +6510,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8198284"/>
+        <c:crossAx val="89593125"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5661,7 +6518,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8198284"/>
+        <c:axId val="89593125"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5705,7 +6562,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21417065"/>
+        <c:crossAx val="50580274"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6344,11 +7201,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="94783334"/>
-        <c:axId val="8846092"/>
+        <c:axId val="62180242"/>
+        <c:axId val="80924187"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="94783334"/>
+        <c:axId val="62180242"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6380,7 +7237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8846092"/>
+        <c:crossAx val="80924187"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6388,7 +7245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8846092"/>
+        <c:axId val="80924187"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6466,7 +7323,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94783334"/>
+        <c:crossAx val="62180242"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6766,11 +7623,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="56944663"/>
-        <c:axId val="27321986"/>
+        <c:axId val="59103199"/>
+        <c:axId val="675415"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="56944663"/>
+        <c:axId val="59103199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6802,7 +7659,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27321986"/>
+        <c:crossAx val="675415"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6810,7 +7667,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27321986"/>
+        <c:axId val="675415"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6854,9 +7711,666 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56944663"/>
+        <c:crossAx val="59103199"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>고3 모의고사+수능 · 총점 (반 평균 = 굵은 선)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!A8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>구성관</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중3 3차 (2025)
+고3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고3 모의고사·수능'!$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!A9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>송지효</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중3 3차 (2025)
+고3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고3 모의고사·수능'!$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!A10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>신준섭</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중3 3차 (2025)
+고3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고3 모의고사·수능'!$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>87</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!A11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>박주연</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7d5fa0"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="7d5fa0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="7d5fa0"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중3 3차 (2025)
+고3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고3 모의고사·수능'!$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>82</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!A12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>반 평균</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:ln w="57240">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>중3 3차 (2025)
+고3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'고3 모의고사·수능'!$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>92.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="73915847"/>
+        <c:axId val="93769188"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="73915847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="93769188"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="93769188"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="50"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>총점</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="73915847"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="10"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -7101,6 +8615,41 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>134640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>332280</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>135720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="3247920"/>
+        <a:ext cx="5759640" cy="3239640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -7364,10 +8913,13 @@
       <c r="E8" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">'고1 모의고사'!B9</f>
@@ -7381,14 +8933,18 @@
         <f aca="false">'고2 모의고사'!I10</f>
         <v>94</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <f aca="false">D9-B9</f>
-        <v>23</v>
+      <c r="E9" s="6" t="n">
+        <f aca="false">'고3 모의고사·수능'!C8</f>
+        <v>100</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <f aca="false">E9-B9</f>
+        <v>29</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">'고1 모의고사'!B10</f>
@@ -7402,14 +8958,18 @@
         <f aca="false">'고2 모의고사'!I11</f>
         <v>91.5</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <f aca="false">D10-B10</f>
-        <v>33.5</v>
+      <c r="E10" s="6" t="n">
+        <f aca="false">'고3 모의고사·수능'!C9</f>
+        <v>100</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <f aca="false">E10-B10</f>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="5" t="n">
         <f aca="false">'고1 모의고사'!B11</f>
@@ -7423,14 +8983,18 @@
         <f aca="false">'고2 모의고사'!I12</f>
         <v>83.5</v>
       </c>
-      <c r="E11" s="7" t="n">
-        <f aca="false">D11-B11</f>
-        <v>13.5</v>
+      <c r="E11" s="6" t="n">
+        <f aca="false">'고3 모의고사·수능'!C10</f>
+        <v>87</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <f aca="false">E11-B11</f>
+        <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">'고1 모의고사'!B12</f>
@@ -7444,14 +9008,18 @@
         <f aca="false">'고2 모의고사'!I13</f>
         <v>78.25</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <f aca="false">D12-B12</f>
-        <v>9.25</v>
+      <c r="E12" s="6" t="n">
+        <f aca="false">'고3 모의고사·수능'!C11</f>
+        <v>82</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <f aca="false">E12-B12</f>
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="9" t="n">
         <f aca="false">'고1 모의고사'!B13</f>
@@ -7465,14 +9033,18 @@
         <f aca="false">'고2 모의고사'!I14</f>
         <v>86.8125</v>
       </c>
-      <c r="E13" s="10" t="n">
-        <f aca="false">D13-B13</f>
-        <v>19.8125</v>
+      <c r="E13" s="9" t="n">
+        <f aca="false">'고3 모의고사·수능'!C12</f>
+        <v>92.25</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <f aca="false">E13-B13</f>
+        <v>25.25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -7507,12 +9079,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -7529,7 +9101,7 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -7546,7 +9118,7 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -7563,7 +9135,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -7583,45 +9155,45 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>71</v>
@@ -7667,7 +9239,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>58</v>
@@ -7713,7 +9285,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>70</v>
@@ -7759,7 +9331,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>69</v>
@@ -7805,7 +9377,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="16" t="n">
         <f aca="false">AVERAGE(B9:B12)</f>
@@ -7858,7 +9430,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -7893,12 +9465,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -7912,7 +9484,7 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -7926,7 +9498,7 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -7940,7 +9512,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -7954,7 +9526,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -7971,36 +9543,36 @@
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>89</v>
@@ -8037,7 +9609,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>92</v>
@@ -8074,7 +9646,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>94</v>
@@ -8111,7 +9683,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>69</v>
@@ -8148,7 +9720,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">AVERAGE(B10:B13)</f>
@@ -8189,7 +9761,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -8209,4 +9781,151 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <f aca="false">AVERAGE(B8:B8)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <f aca="false">AVERAGE(B9:B9)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <f aca="false">AVERAGE(B10:B10)</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <f aca="false">AVERAGE(B11:B11)</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <f aca="false">AVERAGE(B8:B11)</f>
+        <v>92.25</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">AVERAGE(B8:B11)</f>
+        <v>92.25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/output/isabel-cohorts/구성관반_총점_성장.xlsx
+++ b/output/isabel-cohorts/구성관반_총점_성장.xlsx
@@ -11,7 +11,7 @@
     <sheet name="총점 성장 요약" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="고1 모의고사" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="고2 모의고사" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="고3 모의고사·수능" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="고3 모의고사" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -104,24 +104,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수능</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">3(</t>
     </r>
     <r>
       <rPr>
@@ -206,24 +189,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수능 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">92.3</t>
+      <t xml:space="preserve">3 92.3</t>
     </r>
     <r>
       <rPr>
@@ -660,26 +626,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">모의고사</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수능
+      <t xml:space="preserve">모의고사
 평균</t>
     </r>
   </si>
@@ -3605,26 +3552,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">모의고사</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수능 총점 변화</t>
+      <t xml:space="preserve">모의고사 총점 변화</t>
     </r>
   </si>
   <si>
@@ -4105,24 +4033,75 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">차 고</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모의고사는 성적표에 아직 기록이 없습니다</t>
+      <t xml:space="preserve">차</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">학년도 수능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 난이도가 매우 높았던 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">불수능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이라 비교에서 제외했습니다</t>
     </r>
     <r>
       <rPr>
@@ -4644,7 +4623,7 @@
 평균</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>고3 모의고사+수능
+                  <c:v>고3 모의고사
 평균</c:v>
                 </c:pt>
               </c:strCache>
@@ -4674,11 +4653,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="40489550"/>
-        <c:axId val="51854719"/>
+        <c:axId val="34549100"/>
+        <c:axId val="39585498"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40489550"/>
+        <c:axId val="34549100"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4710,7 +4689,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51854719"/>
+        <c:crossAx val="39585498"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4718,7 +4697,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51854719"/>
+        <c:axId val="39585498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4762,7 +4741,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40489550"/>
+        <c:crossAx val="34549100"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5131,7 +5110,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>고3 모의고사+수능
+                  <c:v>고3 모의고사
 평균</c:v>
                 </c:pt>
               </c:strCache>
@@ -5220,11 +5199,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="38058538"/>
-        <c:axId val="8728869"/>
+        <c:axId val="25321474"/>
+        <c:axId val="36902924"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38058538"/>
+        <c:axId val="25321474"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5256,7 +5235,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8728869"/>
+        <c:crossAx val="36902924"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5264,7 +5243,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8728869"/>
+        <c:axId val="36902924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5308,7 +5287,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38058538"/>
+        <c:crossAx val="25321474"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6052,11 +6031,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="91824569"/>
-        <c:axId val="94356926"/>
+        <c:axId val="83833082"/>
+        <c:axId val="33507811"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91824569"/>
+        <c:axId val="83833082"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6088,7 +6067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94356926"/>
+        <c:crossAx val="33507811"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6096,7 +6075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94356926"/>
+        <c:axId val="33507811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6174,7 +6153,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91824569"/>
+        <c:crossAx val="83833082"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6474,11 +6453,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="50580274"/>
-        <c:axId val="89593125"/>
+        <c:axId val="45233979"/>
+        <c:axId val="44955514"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50580274"/>
+        <c:axId val="45233979"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6510,7 +6489,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89593125"/>
+        <c:crossAx val="44955514"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6518,7 +6497,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89593125"/>
+        <c:axId val="44955514"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6562,7 +6541,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50580274"/>
+        <c:crossAx val="45233979"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7201,11 +7180,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="62180242"/>
-        <c:axId val="80924187"/>
+        <c:axId val="39297642"/>
+        <c:axId val="65980245"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="62180242"/>
+        <c:axId val="39297642"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7237,7 +7216,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80924187"/>
+        <c:crossAx val="65980245"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7245,7 +7224,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80924187"/>
+        <c:axId val="65980245"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7323,7 +7302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62180242"/>
+        <c:crossAx val="39297642"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7623,11 +7602,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="59103199"/>
-        <c:axId val="675415"/>
+        <c:axId val="32918874"/>
+        <c:axId val="41865875"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="59103199"/>
+        <c:axId val="32918874"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7659,7 +7638,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="675415"/>
+        <c:crossAx val="41865875"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7667,7 +7646,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="675415"/>
+        <c:axId val="41865875"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7711,7 +7690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59103199"/>
+        <c:crossAx val="32918874"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7789,7 +7768,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>고3 모의고사+수능 · 총점 (반 평균 = 굵은 선)</a:t>
+              <a:t>고3 모의고사 · 총점 (반 평균 = 굵은 선)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -7812,7 +7791,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!A8</c:f>
+              <c:f>'고3 모의고사'!A8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7868,7 +7847,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:f>'고3 모의고사'!$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7880,7 +7859,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고3 모의고사·수능'!$B$8</c:f>
+              <c:f>'고3 모의고사'!$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7897,7 +7876,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!A9</c:f>
+              <c:f>'고3 모의고사'!A9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7953,7 +7932,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:f>'고3 모의고사'!$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7965,7 +7944,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고3 모의고사·수능'!$B$9</c:f>
+              <c:f>'고3 모의고사'!$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -7982,7 +7961,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!A10</c:f>
+              <c:f>'고3 모의고사'!A10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8038,7 +8017,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:f>'고3 모의고사'!$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8050,7 +8029,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고3 모의고사·수능'!$B$10</c:f>
+              <c:f>'고3 모의고사'!$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8067,7 +8046,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!A11</c:f>
+              <c:f>'고3 모의고사'!A11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8123,7 +8102,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:f>'고3 모의고사'!$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8135,7 +8114,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고3 모의고사·수능'!$B$11</c:f>
+              <c:f>'고3 모의고사'!$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8152,7 +8131,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!A12</c:f>
+              <c:f>'고3 모의고사'!A12</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8213,7 +8192,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'고3 모의고사·수능'!$B$7</c:f>
+              <c:f>'고3 모의고사'!$B$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8225,7 +8204,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'고3 모의고사·수능'!$B$12</c:f>
+              <c:f>'고3 모의고사'!$B$12</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="1"/>
@@ -8245,11 +8224,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="73915847"/>
-        <c:axId val="93769188"/>
+        <c:axId val="15799889"/>
+        <c:axId val="37734744"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73915847"/>
+        <c:axId val="15799889"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8281,7 +8260,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93769188"/>
+        <c:crossAx val="37734744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8289,7 +8268,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93769188"/>
+        <c:axId val="37734744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8367,7 +8346,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73915847"/>
+        <c:crossAx val="15799889"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8934,7 +8913,7 @@
         <v>94</v>
       </c>
       <c r="E9" s="6" t="n">
-        <f aca="false">'고3 모의고사·수능'!C8</f>
+        <f aca="false">'고3 모의고사'!C8</f>
         <v>100</v>
       </c>
       <c r="F9" s="7" t="n">
@@ -8959,7 +8938,7 @@
         <v>91.5</v>
       </c>
       <c r="E10" s="6" t="n">
-        <f aca="false">'고3 모의고사·수능'!C9</f>
+        <f aca="false">'고3 모의고사'!C9</f>
         <v>100</v>
       </c>
       <c r="F10" s="7" t="n">
@@ -8984,7 +8963,7 @@
         <v>83.5</v>
       </c>
       <c r="E11" s="6" t="n">
-        <f aca="false">'고3 모의고사·수능'!C10</f>
+        <f aca="false">'고3 모의고사'!C10</f>
         <v>87</v>
       </c>
       <c r="F11" s="7" t="n">
@@ -9009,7 +8988,7 @@
         <v>78.25</v>
       </c>
       <c r="E12" s="6" t="n">
-        <f aca="false">'고3 모의고사·수능'!C11</f>
+        <f aca="false">'고3 모의고사'!C11</f>
         <v>82</v>
       </c>
       <c r="F12" s="7" t="n">
@@ -9034,7 +9013,7 @@
         <v>86.8125</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">'고3 모의고사·수능'!C12</f>
+        <f aca="false">'고3 모의고사'!C12</f>
         <v>92.25</v>
       </c>
       <c r="F13" s="10" t="n">

--- a/output/isabel-cohorts/구성관반_총점_성장.xlsx
+++ b/output/isabel-cohorts/구성관반_총점_성장.xlsx
@@ -172,7 +172,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2 86.8</t>
+      <t xml:space="preserve">2 86.9</t>
     </r>
     <r>
       <rPr>
@@ -2739,7 +2739,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">86.5</t>
+      <t xml:space="preserve">86.8</t>
     </r>
     <r>
       <rPr>
@@ -2756,7 +2756,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(+0.5</t>
+      <t xml:space="preserve">(+0.8</t>
     </r>
     <r>
       <rPr>
@@ -4642,7 +4642,7 @@
                   <c:v>80.3571428571429</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>86.8125</c:v>
+                  <c:v>86.875</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>92.25</c:v>
@@ -4653,11 +4653,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="34549100"/>
-        <c:axId val="39585498"/>
+        <c:axId val="73857026"/>
+        <c:axId val="58816607"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34549100"/>
+        <c:axId val="73857026"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4689,7 +4689,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39585498"/>
+        <c:crossAx val="58816607"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4697,7 +4697,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39585498"/>
+        <c:axId val="58816607"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -4741,7 +4741,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34549100"/>
+        <c:crossAx val="73857026"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5086,7 +5086,7 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>94</c:v>
+                  <c:v>94.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>91.5</c:v>
@@ -5199,11 +5199,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="25321474"/>
-        <c:axId val="36902924"/>
+        <c:axId val="59944633"/>
+        <c:axId val="46426665"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25321474"/>
+        <c:axId val="59944633"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5235,7 +5235,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36902924"/>
+        <c:crossAx val="46426665"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5243,7 +5243,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36902924"/>
+        <c:axId val="46426665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -5287,7 +5287,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25321474"/>
+        <c:crossAx val="59944633"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6031,11 +6031,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="83833082"/>
-        <c:axId val="33507811"/>
+        <c:axId val="99556763"/>
+        <c:axId val="50892429"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83833082"/>
+        <c:axId val="99556763"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6067,7 +6067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33507811"/>
+        <c:crossAx val="50892429"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6075,7 +6075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="33507811"/>
+        <c:axId val="50892429"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6153,7 +6153,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83833082"/>
+        <c:crossAx val="99556763"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -6453,11 +6453,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="45233979"/>
-        <c:axId val="44955514"/>
+        <c:axId val="16106260"/>
+        <c:axId val="10747158"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45233979"/>
+        <c:axId val="16106260"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6489,7 +6489,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44955514"/>
+        <c:crossAx val="10747158"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6497,7 +6497,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44955514"/>
+        <c:axId val="10747158"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -6541,7 +6541,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45233979"/>
+        <c:crossAx val="16106260"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6736,7 +6736,7 @@
                   <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>92</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7165,7 +7165,7 @@
                   <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>86.5</c:v>
+                  <c:v>86.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7180,11 +7180,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="39297642"/>
-        <c:axId val="65980245"/>
+        <c:axId val="60362124"/>
+        <c:axId val="6293685"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39297642"/>
+        <c:axId val="60362124"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7216,7 +7216,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65980245"/>
+        <c:crossAx val="6293685"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7224,7 +7224,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65980245"/>
+        <c:axId val="6293685"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7302,7 +7302,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39297642"/>
+        <c:crossAx val="60362124"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7582,7 +7582,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>92</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>95</c:v>
@@ -7594,7 +7594,7 @@
                   <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>86.5</c:v>
+                  <c:v>86.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7602,11 +7602,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="32918874"/>
-        <c:axId val="41865875"/>
+        <c:axId val="16471504"/>
+        <c:axId val="79847336"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32918874"/>
+        <c:axId val="16471504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7638,7 +7638,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41865875"/>
+        <c:crossAx val="79847336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7646,7 +7646,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41865875"/>
+        <c:axId val="79847336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -7690,7 +7690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32918874"/>
+        <c:crossAx val="16471504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8224,11 +8224,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="15799889"/>
-        <c:axId val="37734744"/>
+        <c:axId val="38964330"/>
+        <c:axId val="93322199"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="15799889"/>
+        <c:axId val="38964330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8260,7 +8260,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37734744"/>
+        <c:crossAx val="93322199"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8268,7 +8268,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37734744"/>
+        <c:axId val="93322199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="100"/>
@@ -8346,7 +8346,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15799889"/>
+        <c:crossAx val="38964330"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">'고2 모의고사'!I10</f>
-        <v>94</v>
+        <v>94.25</v>
       </c>
       <c r="E9" s="6" t="n">
         <f aca="false">'고3 모의고사'!C8</f>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">'고2 모의고사'!I14</f>
-        <v>86.8125</v>
+        <v>86.875</v>
       </c>
       <c r="E13" s="9" t="n">
         <f aca="false">'고3 모의고사'!C12</f>
@@ -9563,7 +9563,7 @@
         <v>95</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F10" s="13" t="n">
         <f aca="false">B10</f>
@@ -9571,15 +9571,15 @@
       </c>
       <c r="G10" s="13" t="n">
         <f aca="false">LOOKUP(9.99E+307,B10:E10)</f>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">G10-F10</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="15" t="n">
         <f aca="false">AVERAGE(B10:E10)</f>
-        <v>94</v>
+        <v>94.25</v>
       </c>
       <c r="J10" s="13" t="n">
         <f aca="false">MAX(B10:E10)</f>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">AVERAGE(E10:E13)</f>
-        <v>86.5</v>
+        <v>86.75</v>
       </c>
       <c r="F14" s="16" t="n">
         <f aca="false">B14</f>
@@ -9723,15 +9723,15 @@
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">E14</f>
-        <v>86.5</v>
+        <v>86.75</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">G14-F14</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I14" s="16" t="n">
         <f aca="false">AVERAGE(B10:E13)</f>
-        <v>86.8125</v>
+        <v>86.875</v>
       </c>
       <c r="J14" s="16" t="n">
         <f aca="false">MAX(B14:E14)</f>
